--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N89_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N89_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.09852210154363</v>
+        <v>7.65350984150084</v>
       </c>
       <c r="D2" t="n">
-        <v>32.67535719630222</v>
+        <v>5.309745544399111</v>
       </c>
       <c r="E2" t="n">
-        <v>17.87439754109249</v>
+        <v>2.90458960042753</v>
       </c>
       <c r="F2" t="n">
-        <v>12.2577535504324</v>
+        <v>1.991884951945265</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.99059051976479</v>
+        <v>5.035970959461778</v>
       </c>
       <c r="D3" t="n">
-        <v>32.08516332507759</v>
+        <v>5.21383904032511</v>
       </c>
       <c r="E3" t="n">
-        <v>17.87439754109249</v>
+        <v>2.90458960042753</v>
       </c>
       <c r="F3" t="n">
-        <v>12.2577535504324</v>
+        <v>1.991884951945265</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.786588435660215</v>
+        <v>0.615320620794785</v>
       </c>
       <c r="D4" t="n">
-        <v>6.382662239720778</v>
+        <v>1.037182613954627</v>
       </c>
       <c r="E4" t="n">
-        <v>17.87439754109249</v>
+        <v>2.90458960042753</v>
       </c>
       <c r="F4" t="n">
-        <v>12.2577535504324</v>
+        <v>1.991884951945265</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
